--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,10 +52,16 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>MM</t>
@@ -64,7 +73,13 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-06-25 11:57:18</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:57:00</t>
+  </si>
+  <si>
+    <t>3233849299 3233849299</t>
   </si>
   <si>
     <t>Общи литри по продукт / МП ЛЕНД ООД</t>
@@ -482,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,14 +506,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -532,45 +550,63 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>55.93</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
         <v>1.77</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>99</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.77</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>99</v>
       </c>
-      <c r="K2" t="s">
-        <v>16</v>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -578,29 +614,29 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="B7" s="6">
         <v>55.93</v>
@@ -618,9 +654,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="9">
         <v>55.93</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,10 +55,19 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>MM</t>
@@ -67,7 +79,25 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-07-03 13:00:45</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>16:39:00</t>
+  </si>
+  <si>
+    <t>09:43:00</t>
+  </si>
+  <si>
+    <t>3234248121 3234248121</t>
+  </si>
+  <si>
+    <t>3235141169 3235141169</t>
+  </si>
+  <si>
+    <t>3235337145 3235337145</t>
   </si>
   <si>
     <t>Общи литри по продукт / МП ЛЕНД ООД</t>
@@ -485,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -494,15 +524,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,116 +571,216 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>51.34</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
         <v>1.76</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>90.36</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.76</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>90.36</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>55.87</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>1.79</v>
+      </c>
+      <c r="I3" s="1">
+        <v>100.01</v>
+      </c>
+      <c r="J3">
+        <v>1.79</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100.01</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>45.79</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>1.82</v>
+      </c>
+      <c r="I4" s="1">
+        <v>83.34</v>
+      </c>
+      <c r="J4">
+        <v>1.82</v>
+      </c>
+      <c r="K4" s="1">
+        <v>83.34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+      <c r="B9" s="6">
+        <v>153</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.789</v>
+      </c>
+      <c r="E9" s="6">
+        <v>273.71</v>
+      </c>
+      <c r="F9" s="6">
+        <v>273.71</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>51.34</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.76</v>
-      </c>
-      <c r="E7" s="6">
-        <v>90.36</v>
-      </c>
-      <c r="F7" s="6">
-        <v>90.36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>51.34</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>90.36</v>
-      </c>
-      <c r="F8" s="9">
-        <v>90.36</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="9">
+        <v>153</v>
+      </c>
+      <c r="C10" s="9">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="9">
+        <v>273.71</v>
+      </c>
+      <c r="F10" s="9">
+        <v>273.71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
@@ -124,7 +124,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="7">
-        <v>1.789</v>
+        <v>1.788954</v>
       </c>
       <c r="E9" s="6">
         <v>273.71</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -515,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -528,13 +531,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,142 +580,154 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>51.34</v>
+        <v>51.341</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2">
         <v>1.76</v>
       </c>
       <c r="I2" s="1">
-        <v>90.36</v>
+        <v>1.76</v>
       </c>
       <c r="J2">
+        <v>90.36015999999999</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.76</v>
       </c>
-      <c r="K2" s="1">
-        <v>90.36</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1">
+        <v>90.36015999999999</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>55.872</v>
+      </c>
+      <c r="G3" t="s">
         <v>22</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>55.87</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
       </c>
       <c r="H3">
         <v>1.79</v>
       </c>
       <c r="I3" s="1">
-        <v>100.01</v>
+        <v>1.79</v>
       </c>
       <c r="J3">
+        <v>100.01088</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.79</v>
       </c>
-      <c r="K3" s="1">
-        <v>100.01</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>100.01088</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>26</v>
+      <c r="O3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>45.79</v>
+        <v>45.791</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4">
         <v>1.82</v>
       </c>
       <c r="I4" s="1">
-        <v>83.34</v>
+        <v>1.82</v>
       </c>
       <c r="J4">
+        <v>83.33962</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.82</v>
       </c>
-      <c r="K4" s="1">
-        <v>83.34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>83.33962</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>27</v>
+      <c r="O4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -720,38 +735,38 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6">
-        <v>153</v>
+        <v>153.004</v>
       </c>
       <c r="C9" s="6">
         <v>3</v>
       </c>
       <c r="D9" s="7">
-        <v>1.788954</v>
+        <v>1.788912</v>
       </c>
       <c r="E9" s="6">
         <v>273.71</v>
@@ -760,12 +775,12 @@
         <v>273.71</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="9">
-        <v>153</v>
+        <v>153.004</v>
       </c>
       <c r="C10" s="9">
         <v>3</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МП ЛЕНД ООД/МП ЛЕНД ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -126,8 +123,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -220,10 +217,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -531,13 +528,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -580,154 +577,142 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
       </c>
       <c r="F2">
         <v>51.341</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>1.76</v>
       </c>
       <c r="I2" s="1">
+        <v>90.36</v>
+      </c>
+      <c r="J2">
         <v>1.76</v>
       </c>
-      <c r="J2">
-        <v>90.36015999999999</v>
-      </c>
       <c r="K2" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L2" s="1">
-        <v>90.36015999999999</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2">
+        <v>90.36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>26</v>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
       </c>
       <c r="F3">
         <v>55.872</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>1.79</v>
       </c>
       <c r="I3" s="1">
+        <v>100.011</v>
+      </c>
+      <c r="J3">
         <v>1.79</v>
       </c>
-      <c r="J3">
-        <v>100.01088</v>
-      </c>
       <c r="K3" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L3" s="1">
-        <v>100.01088</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3">
+        <v>100.011</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>27</v>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
       </c>
       <c r="F4">
         <v>45.791</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4">
         <v>1.82</v>
       </c>
       <c r="I4" s="1">
+        <v>83.34</v>
+      </c>
+      <c r="J4">
         <v>1.82</v>
       </c>
-      <c r="J4">
-        <v>83.33962</v>
-      </c>
       <c r="K4" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L4" s="1">
-        <v>83.33962</v>
-      </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4">
+        <v>83.34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -735,49 +720,49 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="6">
         <v>153.004</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>3</v>
       </c>
       <c r="D9" s="7">
-        <v>1.788912</v>
-      </c>
-      <c r="E9" s="6">
-        <v>273.71</v>
-      </c>
-      <c r="F9" s="6">
-        <v>273.71</v>
+        <v>1.789</v>
+      </c>
+      <c r="E9" s="7">
+        <v>273.711</v>
+      </c>
+      <c r="F9" s="7">
+        <v>273.711</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="9">
         <v>153.004</v>
@@ -787,10 +772,10 @@
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="9">
-        <v>273.71</v>
+        <v>273.711</v>
       </c>
       <c r="F10" s="9">
-        <v>273.71</v>
+        <v>273.711</v>
       </c>
     </row>
   </sheetData>
